--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2444,7 +2444,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104593757</v>
+        <v>104593773</v>
       </c>
       <c r="B16" t="n">
         <v>73471</v>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623427.6496181958</v>
+        <v>623429.0208786447</v>
       </c>
       <c r="R16" t="n">
-        <v>6929266.961572353</v>
+        <v>6929229.978098064</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2557,7 +2557,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104593773</v>
+        <v>104699466</v>
       </c>
       <c r="B17" t="n">
         <v>73471</v>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623429.0208786447</v>
+        <v>623532.0041409323</v>
       </c>
       <c r="R17" t="n">
-        <v>6929229.978098064</v>
+        <v>6929228.242874263</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2628,22 +2628,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-10-19</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-19</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2670,14 +2670,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104699466</v>
+        <v>98306695</v>
       </c>
       <c r="B18" t="n">
-        <v>73471</v>
+        <v>56411</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2686,35 +2686,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>96</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödprick</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Arthonia helvola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Eriksdal 138, Sundsvall, Mpd</t>
+          <t>Nacka, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623532.0041409323</v>
+        <v>623590.4904423348</v>
       </c>
       <c r="R18" t="n">
-        <v>6929228.242874263</v>
+        <v>6929263.744763758</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2741,22 +2751,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2022-01-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2022-01-25</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2771,19 +2781,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>98306695</v>
+        <v>98838317</v>
       </c>
       <c r="B19" t="n">
         <v>56411</v>
@@ -2818,26 +2828,26 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nacka, Sundsvall, Mpd</t>
+          <t>Nacka 107, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623590.4904423348</v>
+        <v>623926.8978685384</v>
       </c>
       <c r="R19" t="n">
-        <v>6929263.744763758</v>
+        <v>6929205.885195598</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2864,22 +2874,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-01-25</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-01-25</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2906,10 +2916,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>98838317</v>
+        <v>117625484</v>
       </c>
       <c r="B20" t="n">
-        <v>56411</v>
+        <v>57687</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2922,45 +2932,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>102122</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flodsångare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Locustella fluviatilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wolf, 1810)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nacka 107, Sundsvall, Mpd</t>
+          <t>Nacka, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623926.8978685384</v>
+        <v>624191</v>
       </c>
       <c r="R20" t="n">
-        <v>6929205.885195598</v>
+        <v>6929390</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2987,22 +2998,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3017,139 +3028,15 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>117625484</v>
-      </c>
-      <c r="B21" t="n">
-        <v>57687</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>102122</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Flodsångare</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Locustella fluviatilis</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Wolf, 1810)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Nacka, Alnö, Mpd</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>624191</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6929390</v>
-      </c>
-      <c r="S21" t="n">
-        <v>25</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Alnö</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Thomas Engström</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Thomas Engström</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3038,6 +3038,122 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128317477</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56979</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nacka, Alnö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>623908</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6929204</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3043,7 +3043,7 @@
         <v>128317477</v>
       </c>
       <c r="B21" t="n">
-        <v>56979</v>
+        <v>56991</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3043,7 +3043,7 @@
         <v>128317477</v>
       </c>
       <c r="B21" t="n">
-        <v>56991</v>
+        <v>56995</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3154,6 +3154,125 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128767522</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57530</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nacka, Alnö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>624293</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6929183</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3159,7 +3159,7 @@
         <v>128767522</v>
       </c>
       <c r="B22" t="n">
-        <v>57530</v>
+        <v>57557</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3043,7 +3043,7 @@
         <v>128317477</v>
       </c>
       <c r="B21" t="n">
-        <v>56995</v>
+        <v>57022</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3159,7 +3159,7 @@
         <v>128767522</v>
       </c>
       <c r="B22" t="n">
-        <v>57564</v>
+        <v>57566</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3159,7 +3159,7 @@
         <v>128767522</v>
       </c>
       <c r="B22" t="n">
-        <v>57566</v>
+        <v>57568</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3273,6 +3273,129 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129724736</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>nacka, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>624322</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6929299</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Piero Crotto</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Piero Crotto</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3278,7 +3278,7 @@
         <v>129724736</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57728</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3278,7 +3278,7 @@
         <v>129724736</v>
       </c>
       <c r="B23" t="n">
-        <v>57728</v>
+        <v>57729</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3512,7 +3512,7 @@
         <v>94188964</v>
       </c>
       <c r="B25" t="n">
-        <v>58348</v>
+        <v>58349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3512,7 +3512,7 @@
         <v>94188964</v>
       </c>
       <c r="B25" t="n">
-        <v>58349</v>
+        <v>58351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3512,7 +3512,7 @@
         <v>94188964</v>
       </c>
       <c r="B25" t="n">
-        <v>58351</v>
+        <v>58352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3626,6 +3626,130 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131542047</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nacka, Alnö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>624293</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6929183</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Trumning</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3631,7 +3631,7 @@
         <v>131542047</v>
       </c>
       <c r="B26" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3631,7 +3631,7 @@
         <v>131542047</v>
       </c>
       <c r="B26" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3869,6 +3869,129 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132451882</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Småbåtshamnen, Nacka, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>623993</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6929482</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3874,7 +3874,7 @@
         <v>132451882</v>
       </c>
       <c r="B28" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3874,7 +3874,7 @@
         <v>132451882</v>
       </c>
       <c r="B28" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3874,7 +3874,7 @@
         <v>132451882</v>
       </c>
       <c r="B28" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3991,6 +3991,111 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132892657</v>
+      </c>
+      <c r="B29" t="n">
+        <v>84149</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nacka, Alnö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>624269</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6929358</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -3997,7 +3997,7 @@
         <v>132892657</v>
       </c>
       <c r="B29" t="n">
-        <v>84156</v>
+        <v>84157</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>102344</v>
       </c>
       <c r="B2" t="n">
-        <v>73470</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623612.9194387216</v>
+        <v>623613</v>
       </c>
       <c r="R2" t="n">
-        <v>6929234.024104427</v>
+        <v>6929234</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2006-09-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-09-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -815,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102361</v>
+        <v>102345</v>
       </c>
       <c r="B3" t="n">
-        <v>73470</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -855,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623650.7798900388</v>
+        <v>623631</v>
       </c>
       <c r="R3" t="n">
-        <v>6929225.708572895</v>
+        <v>6929208</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,24 +868,14 @@
           <t>2006-09-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2006-09-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på bark vid basen av gammal gråal (45 cm dbh, ca 100 år gammal), i gråalsumpskog av högörttyp nära bäck, nära havet, svag nordsluttning</t>
+          <t>sparsam på bark vid basen av levande gråal (29 cm dbh), nordisk stormhatt och nässlor i närheten, i gråalsumpskog av högörttyp nära bäck, nära havet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,16 +900,7 @@
           <t>1 substratenheter # gråal</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>2689</t>
-        </is>
-      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -955,15 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102358</v>
+        <v>102346</v>
       </c>
       <c r="B4" t="n">
-        <v>73470</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623643.2535807833</v>
+        <v>623650</v>
       </c>
       <c r="R4" t="n">
-        <v>6929203.671023278</v>
+        <v>6929222</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1028,24 +984,14 @@
           <t>2006-09-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2006-09-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på bark vid basen av gammal jolster (30 cm dbh, ca 100 år gammal, i gråalsumpskog av högörttyp nära bäck, nära havet</t>
+          <t>sparsam på ganska slät bark vid basen av gråal (25 cm dbh), i gråalsumpskog av högörttyp nära bäck, nära havet, svag nordsluttning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,19 +1013,10 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # jolster</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>2688</t>
-        </is>
-      </c>
+          <t>1 substratenheter # gråal</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1098,12 +1035,7 @@
         <v>102357</v>
       </c>
       <c r="B5" t="n">
-        <v>73470</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623603.8661964544</v>
+        <v>623604</v>
       </c>
       <c r="R5" t="n">
-        <v>6929228.132742411</v>
+        <v>6929228</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1168,19 +1100,9 @@
           <t>2006-09-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2006-09-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1235,15 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102345</v>
+        <v>102358</v>
       </c>
       <c r="B6" t="n">
-        <v>73470</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623631.0276218731</v>
+        <v>623643</v>
       </c>
       <c r="R6" t="n">
-        <v>6929208.309264169</v>
+        <v>6929204</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1308,24 +1225,14 @@
           <t>2006-09-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2006-09-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sparsam på bark vid basen av levande gråal (29 cm dbh), nordisk stormhatt och nässlor i närheten, i gråalsumpskog av högörttyp nära bäck, nära havet</t>
+          <t>på bark vid basen av gammal jolster (30 cm dbh, ca 100 år gammal, i gråalsumpskog av högörttyp nära bäck, nära havet</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,10 +1254,19 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # gråal</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr"/>
+          <t>1 substratenheter # jolster</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>2688</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1369,12 +1285,7 @@
         <v>102359</v>
       </c>
       <c r="B7" t="n">
-        <v>73470</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1406,10 +1317,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623628.0266434158</v>
+        <v>623628</v>
       </c>
       <c r="R7" t="n">
-        <v>6929214.215989185</v>
+        <v>6929214</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1439,19 +1350,9 @@
           <t>2006-09-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2006-09-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1497,15 +1398,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102362</v>
+        <v>102361</v>
       </c>
       <c r="B8" t="n">
-        <v>73470</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623660.6044282799</v>
+        <v>623651</v>
       </c>
       <c r="R8" t="n">
-        <v>6929235.79512764</v>
+        <v>6929226</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1570,24 +1466,14 @@
           <t>2006-09-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2006-09-16</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sparsam på bark på nordsidan vid basen av gråal (17 cm dbh), i gråalsumpskog av högörttyp nära bäck, nära havet, svag nordsluttning</t>
+          <t>på bark vid basen av gammal gråal (45 cm dbh, ca 100 år gammal), i gråalsumpskog av högörttyp nära bäck, nära havet, svag nordsluttning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1612,7 +1498,16 @@
           <t>1 substratenheter # gråal</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>2689</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1628,15 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102346</v>
+        <v>102362</v>
       </c>
       <c r="B9" t="n">
-        <v>73470</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1668,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623650.0085087876</v>
+        <v>623661</v>
       </c>
       <c r="R9" t="n">
-        <v>6929221.513505728</v>
+        <v>6929236</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1701,24 +1591,14 @@
           <t>2006-09-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2006-09-16</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sparsam på ganska slät bark vid basen av gråal (25 cm dbh), i gråalsumpskog av högörttyp nära bäck, nära havet, svag nordsluttning</t>
+          <t>sparsam på bark på nordsidan vid basen av gråal (17 cm dbh), i gråalsumpskog av högörttyp nära bäck, nära havet, svag nordsluttning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1759,58 +1639,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103586832</v>
+        <v>104593738</v>
       </c>
       <c r="B10" t="n">
-        <v>55993</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102967</v>
+        <v>96</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Havstrut</t>
+          <t>Rödprick</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Larus marinus</t>
+          <t>Arthonia helvola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nackaviken , Nacka, Alnö, Mpd</t>
+          <t>Nacka, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623622.3829671646</v>
+        <v>623573</v>
       </c>
       <c r="R10" t="n">
-        <v>6929266.317763388</v>
+        <v>6929204</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1837,22 +1705,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-10-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-10-19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1867,27 +1735,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Rode Nordin</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rode Nordin, Eva Norén</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104593785</v>
+        <v>104593752</v>
       </c>
       <c r="B11" t="n">
-        <v>73471</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1920,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623428.5412491905</v>
+        <v>623435</v>
       </c>
       <c r="R11" t="n">
-        <v>6929267.9204848</v>
+        <v>6929242</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1950,22 +1813,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-10-19</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-19</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1992,15 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104593777</v>
+        <v>104593757</v>
       </c>
       <c r="B12" t="n">
-        <v>73471</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623441.7440183081</v>
+        <v>623427</v>
       </c>
       <c r="R12" t="n">
-        <v>6929261.929067745</v>
+        <v>6929266</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2068,7 +1926,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2078,7 +1936,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2105,15 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104593752</v>
+        <v>104593773</v>
       </c>
       <c r="B13" t="n">
-        <v>73471</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2146,10 +1999,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623434.6108364746</v>
+        <v>623429</v>
       </c>
       <c r="R13" t="n">
-        <v>6929241.758634173</v>
+        <v>6929230</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2176,22 +2029,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-10-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-10-19</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2218,15 +2071,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104593825</v>
+        <v>104593777</v>
       </c>
       <c r="B14" t="n">
-        <v>73471</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2259,10 +2107,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623402.0501733855</v>
+        <v>623442</v>
       </c>
       <c r="R14" t="n">
-        <v>6929282.214881238</v>
+        <v>6929261</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2294,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2304,7 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2331,15 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104593738</v>
+        <v>104593785</v>
       </c>
       <c r="B15" t="n">
-        <v>73471</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,14 +2211,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nacka, Sundsvall, Mpd</t>
+          <t>Eriksdal 138, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623573.2084962714</v>
+        <v>623428</v>
       </c>
       <c r="R15" t="n">
-        <v>6929204.773673021</v>
+        <v>6929268</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2407,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2417,7 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2444,15 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104593773</v>
+        <v>104593825</v>
       </c>
       <c r="B16" t="n">
-        <v>73471</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,10 +2323,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623429.0208786447</v>
+        <v>623402</v>
       </c>
       <c r="R16" t="n">
-        <v>6929229.978098064</v>
+        <v>6929282</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2520,7 +2358,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2530,7 +2368,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2560,12 +2398,7 @@
         <v>104699466</v>
       </c>
       <c r="B17" t="n">
-        <v>73471</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2598,10 +2431,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623532.0041409323</v>
+        <v>623532</v>
       </c>
       <c r="R17" t="n">
-        <v>6929228.242874263</v>
+        <v>6929228</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2670,15 +2503,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>98306695</v>
+        <v>123291378</v>
       </c>
       <c r="B18" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,16 +2514,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2712,19 +2540,20 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nacka, Sundsvall, Mpd</t>
+          <t>Småbåtshamnen, Nacka, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623590.4904423348</v>
+        <v>624034</v>
       </c>
       <c r="R18" t="n">
-        <v>6929263.744763758</v>
+        <v>6929466</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2751,22 +2580,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-01-25</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-01-25</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2781,27 +2610,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>98838317</v>
+        <v>131642580</v>
       </c>
       <c r="B19" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2809,16 +2633,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2828,29 +2652,30 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nacka 107, Sundsvall, Mpd</t>
+          <t>Nacka, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623926.8978685384</v>
+        <v>623908</v>
       </c>
       <c r="R19" t="n">
-        <v>6929205.885195598</v>
+        <v>6929204</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2874,22 +2699,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2904,49 +2729,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117625484</v>
+        <v>98306695</v>
       </c>
       <c r="B20" t="n">
-        <v>57687</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102122</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Flodsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Locustella fluviatilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Wolf, 1810)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2958,20 +2778,19 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nacka, Alnö, Mpd</t>
+          <t>Nacka, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624191</v>
+        <v>623590</v>
       </c>
       <c r="R20" t="n">
-        <v>6929390</v>
+        <v>6929264</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2998,22 +2817,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2022-01-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2022-01-25</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3028,22 +2847,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128317477</v>
+        <v>98838317</v>
       </c>
       <c r="B21" t="n">
-        <v>57022</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,16 +2870,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3070,27 +2889,29 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nacka, Alnö, Mpd</t>
+          <t>Nacka 107, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623908</v>
+        <v>623927</v>
       </c>
       <c r="R21" t="n">
-        <v>6929204</v>
+        <v>6929206</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3114,22 +2935,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3144,22 +2965,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128767522</v>
+        <v>131542047</v>
       </c>
       <c r="B22" t="n">
-        <v>57568</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3167,16 +2988,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3193,7 +3014,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3233,22 +3054,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Trumning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3275,10 +3101,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129724736</v>
+        <v>128317477</v>
       </c>
       <c r="B23" t="n">
-        <v>57732</v>
+        <v>57258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3286,50 +3112,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100110</v>
+        <v>100065</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>nacka, Mpd</t>
+          <t>Nacka, Alnö, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624322</v>
+        <v>623908</v>
       </c>
       <c r="R23" t="n">
-        <v>6929299</v>
+        <v>6929204</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3356,22 +3175,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3386,66 +3205,73 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Piero Crotto</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Piero Crotto</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130943137</v>
+        <v>132451882</v>
       </c>
       <c r="B24" t="n">
-        <v>56246</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>234372</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Coregonus maraena</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Bloch, 1779)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>eDNA</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>bäck N Alnön, Gista, Mpd</t>
+          <t>Småbåtshamnen, Nacka, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623601</v>
+        <v>623993</v>
       </c>
       <c r="R24" t="n">
-        <v>6929218</v>
+        <v>6929482</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3472,12 +3298,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3486,33 +3322,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Oskar Norrgrann</t>
+          <t>Thomas Engström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Oskar Norrgrann</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Fiskinventering med eDNA</t>
-        </is>
-      </c>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>94188964</v>
+        <v>129724736</v>
       </c>
       <c r="B25" t="n">
-        <v>58352</v>
+        <v>57945</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3520,21 +3351,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102992</v>
+        <v>100110</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Näktergal</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Luscinia luscinia</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3543,26 +3374,30 @@
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gistabäcken, Alnö, Mpd</t>
+          <t>nacka, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623585</v>
+        <v>624322</v>
       </c>
       <c r="R25" t="n">
-        <v>6929245</v>
+        <v>6929299</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3586,22 +3421,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-06-11</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-06-11</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3616,22 +3451,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Piero Crotto</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Piero Crotto</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131542047</v>
+        <v>130943171</v>
       </c>
       <c r="B26" t="n">
-        <v>57911</v>
+        <v>56338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3639,46 +3474,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100127</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Öring</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Salmo trutta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nacka, Alnö, Mpd</t>
+          <t>bäck N Alnön, Gista, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624293</v>
+        <v>623601</v>
       </c>
       <c r="R26" t="n">
-        <v>6929183</v>
+        <v>6929218</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3705,27 +3537,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Trumning</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3734,28 +3551,33 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Oskar Norrgrann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Oskar Norrgrann</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Fiskinventering med eDNA</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131642580</v>
+        <v>117625484</v>
       </c>
       <c r="B27" t="n">
-        <v>57961</v>
+        <v>58195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3763,21 +3585,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100048</v>
+        <v>102122</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Flodsångare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Locustella fluviatilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wolf, 1810)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3799,13 +3621,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623908</v>
+        <v>624191</v>
       </c>
       <c r="R27" t="n">
-        <v>6929204</v>
+        <v>6929390</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3829,22 +3651,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3871,27 +3693,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132451882</v>
+        <v>97321744</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>58592</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3901,34 +3723,25 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Småbåtshamnen, Nacka, Mpd</t>
+          <t>Eriksdal 138, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>623993</v>
+        <v>623378</v>
       </c>
       <c r="R28" t="n">
-        <v>6929482</v>
+        <v>6929264</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3952,22 +3765,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2021-11-27</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2021-11-27</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3982,53 +3795,58 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Thomas Engström</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132892657</v>
+        <v>128767522</v>
       </c>
       <c r="B29" t="n">
-        <v>84157</v>
+        <v>57794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>232272</v>
+        <v>102621</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4036,13 +3854,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>624269</v>
+        <v>624293</v>
       </c>
       <c r="R29" t="n">
-        <v>6929358</v>
+        <v>6929183</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4066,12 +3884,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4080,7 +3908,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4096,6 +3923,677 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127058811</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57369</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Småbåtshamnen, Nacka, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>624034</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6929466</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>103586832</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57569</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>102967</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Havstrut</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Larus marinus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nackadalbäckens utlopp , Nacka, Alnö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>623622</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6929266</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Rode Nordin, Eva Norén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>94188964</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58420</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>102992</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Näktergal</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Luscinia luscinia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gistabäcken, Alnö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>623585</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6929245</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-06-11</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-06-11</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132892673</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101974</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nacka, Alnö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>624293</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6929183</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132892657</v>
+      </c>
+      <c r="B34" t="n">
+        <v>84199</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nacka, Alnö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>624269</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6929358</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Thomas Engström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130943137</v>
+      </c>
+      <c r="B35" t="n">
+        <v>56312</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>234372</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sik</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Coregonus maraena</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Bloch, 1779)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>bäck N Alnön, Gista, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>623601</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6929218</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Oskar Norrgrann</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Oskar Norrgrann</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Fiskinventering med eDNA</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50551-2024 artfynd.xlsx
+++ b/artfynd/A 50551-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102344</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102345</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102346</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1154,6 +1174,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102357</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1279,6 +1304,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102358</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1395,6 +1425,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102359</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1520,6 +1555,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102361</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1636,6 +1676,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102362</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1744,6 +1789,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593738</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1852,6 +1902,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593752</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1960,6 +2015,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593757</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2068,6 +2128,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593773</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2176,6 +2241,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593777</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2284,6 +2354,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593785</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2392,6 +2467,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593825</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2500,6 +2580,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104699466</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2619,6 +2704,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123291378</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2738,6 +2828,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131642580</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2856,6 +2951,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98306695</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2974,6 +3074,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98838317</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3098,6 +3203,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131542047</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3214,6 +3324,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128317477</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3337,6 +3452,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132451882</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3460,6 +3580,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129724736</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3571,6 +3696,11 @@
           <t>Fiskinventering med eDNA</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130943171</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3690,6 +3820,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117625484</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3804,6 +3939,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97321744</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3923,6 +4063,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128767522</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4042,6 +4187,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127058811</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4157,6 +4307,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103586832</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4276,6 +4431,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94188964</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4378,6 +4538,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132892673</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4483,6 +4648,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132892657</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4594,8 +4764,49 @@
           <t>Fiskinventering med eDNA</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130943137</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>